--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484305_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484305_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8041</v>
+        <v>2.088</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0709</v>
+        <v>3.2731</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2668</v>
+        <v>-1.1851</v>
       </c>
       <c r="G2" t="n">
         <v>1.48</v>
@@ -610,13 +610,13 @@
         <v>0.586</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.06660000000000001</v>
+        <v>0.2174</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0138</v>
+        <v>0.216</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0803</v>
+        <v>0.0014</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8935999999999999</v>
+        <v>0.5516</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3984</v>
+        <v>0.9705</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5047</v>
+        <v>-0.4188</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.8551</v>
+        <v>1.0168</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0338</v>
+        <v>2.3656</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.8889</v>
+        <v>-1.3488</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2957</v>
+        <v>1.9059</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9698</v>
+        <v>2.58</v>
       </c>
       <c r="L3" t="n">
         <v>-0.6741</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.1508</v>
+        <v>-0.8891</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.936</v>
+        <v>-0.2144</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2148</v>
+        <v>-0.6747</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1865</v>
+        <v>0.769</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7556</v>
+        <v>0.2367</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5691000000000001</v>
+        <v>0.5323</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5623</v>
+        <v>-1.4294</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0664</v>
+        <v>-1.4294</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>R. PALOMARES MUÑOZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4891</v>
+        <v>0.3938</v>
       </c>
       <c r="E4" t="n">
-        <v>0.445</v>
+        <v>3.2386</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0442</v>
+        <v>-2.8448</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0168</v>
+        <v>1.1341</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3656</v>
+        <v>-0.0386</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.3488</v>
+        <v>1.1727</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9059</v>
+        <v>4.0102</v>
       </c>
       <c r="K4" t="n">
-        <v>2.58</v>
+        <v>2.0274</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6741</v>
+        <v>1.9828</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8891</v>
+        <v>-2.8761</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2144</v>
+        <v>-2.066</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6747</v>
+        <v>-0.8101</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1721</v>
+        <v>-1.3674</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7064</v>
+        <v>0.1933</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2888</v>
+        <v>0.3186</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9953</v>
+        <v>-0.1253</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.4294</v>
+        <v>-0.5429</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4294</v>
+        <v>-0.8201000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0354</v>
+        <v>-0.0486</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0165</v>
+        <v>1.2654</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.981</v>
+        <v>-1.3141</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1341</v>
+        <v>-1.8551</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0386</v>
+        <v>0.0338</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1727</v>
+        <v>-1.8889</v>
       </c>
       <c r="J5" t="n">
-        <v>4.0102</v>
+        <v>1.2957</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0274</v>
+        <v>1.9698</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9828</v>
+        <v>-0.6741</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.8761</v>
+        <v>-3.1508</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.066</v>
+        <v>-1.936</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8101</v>
+        <v>-1.2148</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3674</v>
+        <v>-2.1488</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1651</v>
+        <v>0.2442</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0964</v>
+        <v>0.6227</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2615</v>
+        <v>-0.3785</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5429</v>
+        <v>1.5623</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2772</v>
+        <v>1.4959</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8201000000000001</v>
+        <v>0.0664</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. TURNQUEST</t>
+          <t>J. BERTOMEU BALDÉ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3481</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0401</v>
+        <v>-0.7611</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.308</v>
+        <v>0.6766</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2154</v>
+        <v>-1.7855</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.189</v>
+        <v>-0.8414</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4045</v>
+        <v>-0.9441000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0205</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0205</v>
+        <v>-0.2226</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.6741</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1949</v>
+        <v>-0.8889</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2095</v>
+        <v>-0.6188</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4045</v>
+        <v>-0.27</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5635</v>
+        <v>0.3336</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0605</v>
+        <v>0.1356</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.503</v>
+        <v>0.1981</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BERTOMEU BALDÉ</t>
+          <t>E. TURNQUEST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6118</v>
+        <v>-0.1925</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.125</v>
+        <v>0.0611</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5132</v>
+        <v>-0.2535</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7855</v>
+        <v>0.2154</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8414</v>
+        <v>-0.189</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9441000000000001</v>
+        <v>0.4045</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8967000000000001</v>
+        <v>0.0205</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2226</v>
+        <v>0.0205</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6741</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8889</v>
+        <v>0.1949</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6188</v>
+        <v>-0.2095</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.27</v>
+        <v>0.4045</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1937</v>
+        <v>-0.4079</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2283</v>
+        <v>0.0406</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0346</v>
+        <v>-0.4485</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>P. MARTÍNEZ SERRANO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9073</v>
+        <v>-1.5698</v>
       </c>
       <c r="E8" t="n">
-        <v>0.863</v>
+        <v>-1.0842</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7704</v>
+        <v>-0.4856</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1976</v>
+        <v>-0.0704</v>
       </c>
       <c r="H8" t="n">
-        <v>1.547</v>
+        <v>-0.2865</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3494</v>
+        <v>0.2161</v>
       </c>
       <c r="J8" t="n">
-        <v>2.255</v>
+        <v>-0.1109</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9291</v>
+        <v>0.6165</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6741</v>
+        <v>-0.7274</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0575</v>
+        <v>0.0405</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3822</v>
+        <v>-0.903</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6753</v>
+        <v>0.9435</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1721</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1488</v>
+        <v>-3.1255</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4966</v>
+        <v>-0.0186</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7567</v>
+        <v>0.3791</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7398</v>
+        <v>-0.3977</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4294</v>
+        <v>0.2772</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4294</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ SERRANO</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8616</v>
+        <v>-2.0739</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1853</v>
+        <v>0.3774</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6763</v>
+        <v>-2.4512</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0704</v>
+        <v>0.1976</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2865</v>
+        <v>1.547</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2161</v>
+        <v>-1.3494</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1109</v>
+        <v>2.255</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6165</v>
+        <v>2.9291</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7274</v>
+        <v>-0.6741</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0405</v>
+        <v>-2.0575</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.903</v>
+        <v>-1.3822</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9435</v>
+        <v>-0.6753</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7581</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1255</v>
+        <v>-2.1488</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3103</v>
+        <v>0.3301</v>
       </c>
       <c r="T9" t="n">
-        <v>0.278</v>
+        <v>0.2711</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5883</v>
+        <v>0.059</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2772</v>
+        <v>-1.4294</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7731</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4959</v>
+        <v>-1.4294</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8453</v>
+        <v>-4.8526</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9479</v>
+        <v>-2.9279</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8974</v>
+        <v>-1.9246</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3068</v>
@@ -1234,13 +1234,13 @@
         <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1943</v>
+        <v>-0.2016</v>
       </c>
       <c r="T10" t="n">
-        <v>0.278</v>
+        <v>0.2979</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4723</v>
+        <v>-0.4995</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.7934</v>
+        <v>-6.1183</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.7325</v>
+        <v>-5.1664</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0609</v>
+        <v>-0.952</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7834</v>
@@ -1312,13 +1312,13 @@
         <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.197</v>
+        <v>0.478</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0935</v>
+        <v>0.4726</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1035</v>
+        <v>0.0054</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8828</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.8075</v>
+        <v>-6.138</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5669</v>
+        <v>-2.1425</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.2406</v>
+        <v>-3.9955</v>
       </c>
       <c r="G12" t="n">
         <v>-4.3843</v>
@@ -1390,13 +1390,13 @@
         <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8601</v>
+        <v>-0.1905</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4704</v>
+        <v>-0.046</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3896</v>
+        <v>-0.1445</v>
       </c>
       <c r="V12" t="n">
         <v>1.5623</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-18.9528</v>
+        <v>-18.0448</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.803899999999998</v>
+        <v>-2.896000000000003</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.1487</v>
+        <v>-15.1486</v>
       </c>
       <c r="G13" t="n">
         <v>-8.1416</v>
@@ -1468,13 +1468,13 @@
         <v>11.7206</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8389000000000001</v>
+        <v>1.747</v>
       </c>
       <c r="T13" t="n">
-        <v>2.036999999999999</v>
+        <v>2.9449</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1979</v>
+        <v>-1.1978</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8827</v>
@@ -1483,13 +1483,13 @@
         <v>5.2645</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.147200000000001</v>
+        <v>-7.1472</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. SIMON</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8844</v>
+        <v>4.0571</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0902</v>
+        <v>2.5635</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2058</v>
+        <v>1.4935</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6348</v>
+        <v>3.0544</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7138</v>
+        <v>0.8294</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3486</v>
+        <v>2.225</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3571</v>
+        <v>3.8325</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3338</v>
+        <v>2.4162</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0233</v>
+        <v>1.4163</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7223</v>
+        <v>-0.7781</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0476</v>
+        <v>-1.5868</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6747</v>
+        <v>0.8087</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1953</v>
+        <v>0.1953</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7581</v>
+        <v>3.1255</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0076</v>
+        <v>-0.1341</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2493</v>
+        <v>-0.112</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2417</v>
+        <v>-0.0221</v>
       </c>
       <c r="V14" t="n">
-        <v>2.4373</v>
+        <v>0.9414</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4373</v>
+        <v>1.7731</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.8317</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>N. DEL VAL GARCIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3493</v>
+        <v>3.1479</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2602</v>
+        <v>3.4063</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0891</v>
+        <v>-0.2584</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0544</v>
+        <v>1.777</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8294</v>
+        <v>0.7644</v>
       </c>
       <c r="I15" t="n">
-        <v>2.225</v>
+        <v>1.0126</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8325</v>
+        <v>3.7687</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4162</v>
+        <v>2.6209</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4163</v>
+        <v>1.1478</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7781</v>
+        <v>-1.9917</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5868</v>
+        <v>-1.8565</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8087</v>
+        <v>-0.1352</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1255</v>
+        <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8419</v>
+        <v>-0.3872</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4153</v>
+        <v>-0.3624</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4266</v>
+        <v>-0.0248</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7731</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>A. SIMON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6873</v>
+        <v>3.0288</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1122</v>
+        <v>3.1802</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5750999999999999</v>
+        <v>-0.1514</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1116</v>
+        <v>0.6348</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9921</v>
+        <v>-0.7138</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.1036</v>
+        <v>1.3486</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3267</v>
+        <v>2.3571</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6206</v>
+        <v>0.3338</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2939</v>
+        <v>2.0233</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4382</v>
+        <v>-1.7223</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-1.0476</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8097</v>
+        <v>-0.6747</v>
       </c>
       <c r="P16" t="n">
-        <v>0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5395</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8304</v>
+        <v>0.152</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3565</v>
+        <v>0.3392</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5261</v>
+        <v>-0.1872</v>
       </c>
       <c r="V16" t="n">
-        <v>2.3824</v>
+        <v>2.4373</v>
       </c>
       <c r="W16" t="n">
-        <v>2.3824</v>
+        <v>2.4373</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. DEL VAL GARCIA</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6552</v>
+        <v>2.5916</v>
       </c>
       <c r="E17" t="n">
-        <v>3.103</v>
+        <v>1.8178</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4477</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>1.777</v>
+        <v>2.3246</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7644</v>
+        <v>1.8514</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0126</v>
+        <v>0.4732</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7687</v>
+        <v>2.9628</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6209</v>
+        <v>3.0289</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1478</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9917</v>
+        <v>-0.6382</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8565</v>
+        <v>-1.1775</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1352</v>
+        <v>0.5393</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7581</v>
+        <v>0.7814</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
         <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8799</v>
+        <v>0.095</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6657</v>
+        <v>0.1638</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2141</v>
+        <v>-0.0689</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. SIMS SERRA</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5343</v>
+        <v>2.3869</v>
       </c>
       <c r="E18" t="n">
-        <v>4.1108</v>
+        <v>-0.1094</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5764</v>
+        <v>2.4964</v>
       </c>
       <c r="G18" t="n">
-        <v>3.9412</v>
+        <v>0.657</v>
       </c>
       <c r="H18" t="n">
-        <v>2.12</v>
+        <v>0.4948</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8212</v>
+        <v>0.1623</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1703</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8882</v>
+        <v>0.5142</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2821</v>
+        <v>0.0276</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2291</v>
+        <v>0.1152</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7682</v>
+        <v>-0.0194</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5391</v>
+        <v>0.1346</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9301</v>
+        <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5729</v>
+        <v>0.7532</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2493</v>
+        <v>0.3255</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6764</v>
+        <v>0.4277</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.9331</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.601</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.2804</v>
+        <v>2.2199</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6156</v>
+        <v>1.2173</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6647999999999999</v>
+        <v>1.0026</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3246</v>
+        <v>-2.1999</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8514</v>
+        <v>-0.1095</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4732</v>
+        <v>-2.0904</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9628</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>3.0289</v>
+        <v>1.068</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-1.1459</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6382</v>
+        <v>-2.1221</v>
       </c>
       <c r="N19" t="n">
         <v>-1.1775</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5393</v>
+        <v>-0.9445</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7814</v>
+        <v>3.5162</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7581</v>
+        <v>3.5162</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2162</v>
+        <v>-0.0378</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0384</v>
+        <v>0.0765</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1778</v>
+        <v>-0.1143</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6093</v>
+        <v>0.9414</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3321</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
         <v>-0.2772</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.0305</v>
+        <v>2.1623</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4128</v>
+        <v>1.1011</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4432</v>
+        <v>1.0612</v>
       </c>
       <c r="G20" t="n">
-        <v>0.657</v>
+        <v>-1.1116</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4948</v>
+        <v>0.9921</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1623</v>
+        <v>-2.1036</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.3267</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5142</v>
+        <v>1.6206</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0276</v>
+        <v>-1.2939</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1152</v>
+        <v>-1.4382</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0194</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1346</v>
+        <v>-0.8097</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9534</v>
+        <v>2.5395</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3967</v>
+        <v>0.3054</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0221</v>
+        <v>0.3454</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3746</v>
+        <v>-0.04</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2.3824</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.3824</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>E. SIMS SERRA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9585</v>
+        <v>1.9134</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3072</v>
+        <v>3.3018</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6513</v>
+        <v>-1.3885</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1999</v>
+        <v>3.9412</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1095</v>
+        <v>2.12</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0904</v>
+        <v>1.8212</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.07779999999999999</v>
+        <v>4.1703</v>
       </c>
       <c r="K21" t="n">
-        <v>1.068</v>
+        <v>2.8882</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.1459</v>
+        <v>1.2821</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1221</v>
+        <v>-0.2291</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1775</v>
+        <v>-0.7682</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9445</v>
+        <v>0.5391</v>
       </c>
       <c r="P21" t="n">
-        <v>3.5162</v>
+        <v>1.9534</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>3.5162</v>
+        <v>2.9301</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2992</v>
+        <v>-0.0481</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8335</v>
+        <v>0.4404</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4656</v>
+        <v>-0.4885</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9414</v>
+        <v>-3.9331</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2186</v>
+        <v>-0.3321</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2772</v>
+        <v>-3.601</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4272</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0376</v>
+        <v>-1.3298</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.797</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9358</v>
@@ -2170,13 +2170,13 @@
         <v>2.1488</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4095</v>
+        <v>0.4849</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.0185</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3168</v>
+        <v>0.5034</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2772</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>18.9527</v>
+        <v>20.9751</v>
       </c>
       <c r="E23" t="n">
         <v>15.1488</v>
       </c>
       <c r="F23" t="n">
-        <v>3.804</v>
+        <v>5.826099999999999</v>
       </c>
       <c r="G23" t="n">
         <v>8.1417</v>
@@ -2227,7 +2227,7 @@
         <v>14.4716</v>
       </c>
       <c r="L23" t="n">
-        <v>4.052499999999999</v>
+        <v>4.0525</v>
       </c>
       <c r="M23" t="n">
         <v>-10.3824</v>
@@ -2248,19 +2248,19 @@
         <v>21.4878</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8390999999999997</v>
+        <v>1.1833</v>
       </c>
       <c r="T23" t="n">
-        <v>1.198</v>
+        <v>1.1979</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.0369</v>
+        <v>-0.01470000000000005</v>
       </c>
       <c r="V23" t="n">
-        <v>1.882900000000001</v>
+        <v>1.8829</v>
       </c>
       <c r="W23" t="n">
-        <v>7.147200000000001</v>
+        <v>7.1472</v>
       </c>
       <c r="X23" t="n">
         <v>-5.2643</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484305_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484305_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,7 +563,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -626,84 +631,94 @@
       </c>
       <c r="X2" t="n">
         <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>J. BERTOMEU BALDÉ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5516</v>
+        <v>0.921</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9705</v>
+        <v>0.921</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4188</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0168</v>
+        <v>0.921</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3656</v>
+        <v>0.921</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.3488</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9059</v>
+        <v>0.921</v>
       </c>
       <c r="K3" t="n">
-        <v>2.58</v>
+        <v>0.921</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6741</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8891</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2144</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6747</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.769</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2367</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5323</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.4294</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4294</v>
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -714,230 +729,245 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3938</v>
+        <v>0.607</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2386</v>
+        <v>0.607</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.8448</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1341</v>
+        <v>0.607</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0386</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1727</v>
+        <v>0.607</v>
       </c>
       <c r="J4" t="n">
-        <v>4.0102</v>
+        <v>0.607</v>
       </c>
       <c r="K4" t="n">
-        <v>2.0274</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9828</v>
+        <v>0.607</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.8761</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.066</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8101</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1933</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3186</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1253</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5429</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8201000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0486</v>
+        <v>0.5516</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2654</v>
+        <v>0.9705</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3141</v>
+        <v>-0.4188</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.8551</v>
+        <v>1.0168</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0338</v>
+        <v>2.3656</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8889</v>
+        <v>-1.3488</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2957</v>
+        <v>1.9059</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9698</v>
+        <v>2.58</v>
       </c>
       <c r="L5" t="n">
         <v>-0.6741</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.1508</v>
+        <v>-0.8891</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.936</v>
+        <v>-0.2144</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2148</v>
+        <v>-0.6747</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2442</v>
+        <v>0.769</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6227</v>
+        <v>0.2367</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3785</v>
+        <v>0.5323</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5623</v>
+        <v>-1.4294</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0664</v>
+        <v>-1.4294</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BERTOMEU BALDÉ</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.0486</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7611</v>
+        <v>1.2654</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6766</v>
+        <v>-1.3141</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.7855</v>
+        <v>-1.8551</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8414</v>
+        <v>0.0338</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9441000000000001</v>
+        <v>-1.8889</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8967000000000001</v>
+        <v>1.2957</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2226</v>
+        <v>1.9698</v>
       </c>
       <c r="L6" t="n">
         <v>-0.6741</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8889</v>
+        <v>-3.1508</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6188</v>
+        <v>-1.936</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.27</v>
+        <v>-1.2148</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3336</v>
+        <v>0.2442</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1356</v>
+        <v>0.6227</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1981</v>
+        <v>-0.3785</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.5623</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.0664</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -948,7 +978,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1016,636 +1046,677 @@
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ SERRANO</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5698</v>
+        <v>-0.2132</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0842</v>
+        <v>2.6316</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4856</v>
+        <v>-2.8448</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0704</v>
+        <v>0.5271</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2865</v>
+        <v>-0.0386</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2161</v>
+        <v>0.5657</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1109</v>
+        <v>3.4032</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6165</v>
+        <v>2.0274</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7274</v>
+        <v>1.3758</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0405</v>
+        <v>-2.8761</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.903</v>
+        <v>-2.066</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9435</v>
+        <v>-0.8101</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.7581</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1255</v>
+        <v>-1.3674</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0186</v>
+        <v>0.1933</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3791</v>
+        <v>0.3186</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3977</v>
+        <v>-0.1253</v>
       </c>
       <c r="V8" t="n">
+        <v>-0.5429</v>
+      </c>
+      <c r="W8" t="n">
         <v>0.2772</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.7731</v>
-      </c>
       <c r="X8" t="n">
-        <v>-1.4959</v>
+        <v>-0.8201000000000001</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>J. BERTOMEU BALDE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0739</v>
+        <v>-1.0055</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3774</v>
+        <v>-1.6821</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4512</v>
+        <v>0.6766</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1976</v>
+        <v>-2.7065</v>
       </c>
       <c r="H9" t="n">
-        <v>1.547</v>
+        <v>-1.7624</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3494</v>
+        <v>-0.9441000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>2.255</v>
+        <v>-1.8176</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9291</v>
+        <v>-1.1435</v>
       </c>
       <c r="L9" t="n">
         <v>-0.6741</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0575</v>
+        <v>-0.8889</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3822</v>
+        <v>-0.6188</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6753</v>
+        <v>-0.27</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3301</v>
+        <v>0.3336</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2711</v>
+        <v>0.1356</v>
       </c>
       <c r="U9" t="n">
-        <v>0.059</v>
+        <v>0.1981</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4294</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4294</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>P. MARTINEZ SERRANO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8526</v>
+        <v>-1.5698</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9279</v>
+        <v>-1.0842</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9246</v>
+        <v>-0.4856</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3068</v>
+        <v>-0.0704</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9286</v>
+        <v>-0.2865</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3782</v>
+        <v>0.2161</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1004</v>
+        <v>-0.1109</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4119</v>
+        <v>0.6165</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5122</v>
+        <v>-0.7274</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2065</v>
+        <v>0.0405</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.3405</v>
+        <v>-0.903</v>
       </c>
       <c r="O10" t="n">
-        <v>0.134</v>
+        <v>0.9435</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.3441</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q10" t="n">
         <v>-3.1255</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2016</v>
+        <v>-0.0186</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2979</v>
+        <v>0.3791</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4995</v>
+        <v>-0.3977</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.1183</v>
+        <v>-2.0739</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.1664</v>
+        <v>0.3774</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.952</v>
+        <v>-2.4512</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7834</v>
+        <v>0.1976</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.5521</v>
+        <v>1.547</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7687</v>
+        <v>-1.3494</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1499</v>
+        <v>2.255</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2446</v>
+        <v>2.9291</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09470000000000001</v>
+        <v>-0.6741</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-2.0575</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3075</v>
+        <v>-1.3822</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6739000000000001</v>
+        <v>-0.6753</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.9301</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.1022</v>
+        <v>-2.1488</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>0.478</v>
+        <v>0.3301</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4726</v>
+        <v>0.2711</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0054</v>
+        <v>0.059</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8828</v>
+        <v>-1.4294</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4959</v>
+        <v>-1.4294</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.138</v>
+        <v>-4.8526</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1425</v>
+        <v>-2.9279</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.9955</v>
+        <v>-1.9246</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.3843</v>
+        <v>-2.3068</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6324</v>
+        <v>-1.9286</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.7519</v>
+        <v>-0.3782</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.1004</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4937</v>
+        <v>0.4119</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.5122</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.2848</v>
+        <v>-2.2065</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.1261</v>
+        <v>-2.3405</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.1587</v>
+        <v>0.134</v>
       </c>
       <c r="P12" t="n">
+        <v>-2.3441</v>
+      </c>
+      <c r="Q12" t="n">
         <v>-3.1255</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-4.1022</v>
-      </c>
       <c r="R12" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1905</v>
+        <v>-0.2016</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.046</v>
+        <v>0.2979</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1445</v>
+        <v>-0.4995</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5623</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.1052</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5429</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-18.0448</v>
+        <v>-6.1183</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.896000000000003</v>
+        <v>-5.1664</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.1486</v>
+        <v>-0.952</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.1416</v>
+        <v>-1.7834</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.4411</v>
+        <v>-2.5521</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.7004</v>
+        <v>0.7687</v>
       </c>
       <c r="J13" t="n">
-        <v>10.3824</v>
+        <v>-1.1499</v>
       </c>
       <c r="K13" t="n">
-        <v>9.0304</v>
+        <v>-1.2446</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3521</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-18.5244</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-14.4716</v>
+        <v>-1.3075</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.0526</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-9.767200000000001</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q13" t="n">
-        <v>-21.4878</v>
+        <v>-4.1022</v>
       </c>
       <c r="R13" t="n">
-        <v>11.7206</v>
+        <v>1.1721</v>
       </c>
       <c r="S13" t="n">
-        <v>1.747</v>
+        <v>0.478</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9449</v>
+        <v>0.4726</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1978</v>
+        <v>0.0054</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.8827</v>
+        <v>-1.8828</v>
       </c>
       <c r="W13" t="n">
-        <v>5.2645</v>
+        <v>-0.3869</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.1472</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0571</v>
+        <v>-6.138</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5635</v>
+        <v>-2.1425</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4935</v>
+        <v>-3.9955</v>
       </c>
       <c r="G14" t="n">
-        <v>3.0544</v>
+        <v>-4.3843</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8294</v>
+        <v>-1.6324</v>
       </c>
       <c r="I14" t="n">
-        <v>2.225</v>
+        <v>-2.7519</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8325</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4162</v>
+        <v>0.4937</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4163</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7781</v>
+        <v>-4.2848</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5868</v>
+        <v>-2.1261</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8087</v>
+        <v>-2.1587</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1953</v>
+        <v>-3.1255</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9301</v>
+        <v>-4.1022</v>
       </c>
       <c r="R14" t="n">
-        <v>3.1255</v>
+        <v>0.9767</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1341</v>
+        <v>-0.1905</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.112</v>
+        <v>-0.046</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0221</v>
+        <v>-0.1445</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9414</v>
+        <v>1.5623</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7731</v>
+        <v>2.1052</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8317</v>
+        <v>-0.5429</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. DEL VAL GARCIA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1479</v>
+        <v>-18.0448</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4063</v>
+        <v>-2.896000000000002</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2584</v>
+        <v>-15.1486</v>
       </c>
       <c r="G15" t="n">
-        <v>1.777</v>
+        <v>-8.1416</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7644</v>
+        <v>-5.4411</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0126</v>
+        <v>-2.7004</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7687</v>
+        <v>10.3825</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6209</v>
+        <v>9.0305</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1478</v>
+        <v>1.352099999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9917</v>
+        <v>-18.5244</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8565</v>
+        <v>-14.4716</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1352</v>
+        <v>-4.0526</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7581</v>
+        <v>-9.767200000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-21.4878</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>11.7206</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3872</v>
+        <v>1.747</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3624</v>
+        <v>2.9449</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0248</v>
+        <v>-1.1978</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.8827</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>5.2645</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
-      </c>
+        <v>-7.147200000000001</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SIMON</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0288</v>
+        <v>4.0571</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1802</v>
+        <v>2.5635</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1514</v>
+        <v>1.4935</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6348</v>
+        <v>3.0544</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7138</v>
+        <v>0.8294</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3486</v>
+        <v>2.225</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3571</v>
+        <v>3.8325</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3338</v>
+        <v>2.4162</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0233</v>
+        <v>1.4163</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7223</v>
+        <v>-0.7781</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0476</v>
+        <v>-1.5868</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6747</v>
+        <v>0.8087</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1953</v>
+        <v>0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7581</v>
+        <v>3.1255</v>
       </c>
       <c r="S16" t="n">
-        <v>0.152</v>
+        <v>-0.1341</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3392</v>
+        <v>-0.112</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1872</v>
+        <v>-0.0221</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4373</v>
+        <v>0.9414</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4373</v>
+        <v>1.7731</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>N. DEL VAL GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5916</v>
+        <v>3.1479</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8178</v>
+        <v>3.4063</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7737000000000001</v>
+        <v>-0.2584</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3246</v>
+        <v>1.777</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8514</v>
+        <v>0.7644</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4732</v>
+        <v>1.0126</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9628</v>
+        <v>3.7687</v>
       </c>
       <c r="K17" t="n">
-        <v>3.0289</v>
+        <v>2.6209</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.06610000000000001</v>
+        <v>1.1478</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6382</v>
+        <v>-1.9917</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1775</v>
+        <v>-1.8565</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5393</v>
+        <v>-0.1352</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>0.095</v>
+        <v>-0.3872</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1638</v>
+        <v>-0.3624</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0689</v>
+        <v>-0.0248</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>A. SIMON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3869</v>
+        <v>3.0288</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1094</v>
+        <v>3.1802</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4964</v>
+        <v>-0.1514</v>
       </c>
       <c r="G18" t="n">
-        <v>0.657</v>
+        <v>0.6348</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4948</v>
+        <v>-0.7138</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1623</v>
+        <v>1.3486</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5417999999999999</v>
+        <v>2.3571</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5142</v>
+        <v>0.3338</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0276</v>
+        <v>2.0233</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1152</v>
+        <v>-1.7223</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0194</v>
+        <v>-1.0476</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1346</v>
+        <v>-0.6747</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9534</v>
+        <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7532</v>
+        <v>0.152</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3255</v>
+        <v>0.3392</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4277</v>
+        <v>-0.1872</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.2199</v>
+        <v>2.5916</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2173</v>
+        <v>1.8178</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0026</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1999</v>
+        <v>2.3246</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1095</v>
+        <v>1.8514</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0904</v>
+        <v>0.4732</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.07779999999999999</v>
+        <v>2.9628</v>
       </c>
       <c r="K19" t="n">
-        <v>1.068</v>
+        <v>3.0289</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1459</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1221</v>
+        <v>-0.6382</v>
       </c>
       <c r="N19" t="n">
         <v>-1.1775</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9445</v>
+        <v>0.5393</v>
       </c>
       <c r="P19" t="n">
-        <v>3.5162</v>
+        <v>0.7814</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>3.5162</v>
+        <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0378</v>
+        <v>0.095</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0765</v>
+        <v>0.1638</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1143</v>
+        <v>-0.0689</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9414</v>
+        <v>-0.6093</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>-0.3321</v>
       </c>
       <c r="X19" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.1623</v>
+        <v>2.3869</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1011</v>
+        <v>-0.1094</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0612</v>
+        <v>2.4964</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1116</v>
+        <v>0.657</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9921</v>
+        <v>0.4948</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.1036</v>
+        <v>0.1623</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3267</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6206</v>
+        <v>0.5142</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2939</v>
+        <v>0.0276</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4382</v>
+        <v>0.1152</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.0194</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8097</v>
+        <v>0.1346</v>
       </c>
       <c r="P20" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5395</v>
+        <v>1.9534</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3054</v>
+        <v>0.7532</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3454</v>
+        <v>0.3255</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.04</v>
+        <v>0.4277</v>
       </c>
       <c r="V20" t="n">
-        <v>2.3824</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.3824</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. SIMS SERRA</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.9134</v>
+        <v>2.2199</v>
       </c>
       <c r="E21" t="n">
-        <v>3.3018</v>
+        <v>1.2173</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3885</v>
+        <v>1.0026</v>
       </c>
       <c r="G21" t="n">
-        <v>3.9412</v>
+        <v>-2.1999</v>
       </c>
       <c r="H21" t="n">
-        <v>2.12</v>
+        <v>-0.1095</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8212</v>
+        <v>-2.0904</v>
       </c>
       <c r="J21" t="n">
-        <v>4.1703</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>2.8882</v>
+        <v>1.068</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2821</v>
+        <v>-1.1459</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2291</v>
+        <v>-2.1221</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7682</v>
+        <v>-1.1775</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5391</v>
+        <v>-0.9445</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9534</v>
+        <v>3.5162</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.9301</v>
+        <v>3.5162</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0481</v>
+        <v>-0.0378</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4404</v>
+        <v>0.0765</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4885</v>
+        <v>-0.1143</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.9331</v>
+        <v>0.9414</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3321</v>
+        <v>1.2186</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.601</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5328000000000001</v>
+        <v>2.1623</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3298</v>
+        <v>1.1011</v>
       </c>
       <c r="F22" t="n">
-        <v>0.797</v>
+        <v>1.0612</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9358</v>
+        <v>-1.1116</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7874</v>
+        <v>0.9921</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1484</v>
+        <v>-2.1036</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6421</v>
+        <v>0.3267</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0192</v>
+        <v>1.6206</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6613</v>
+        <v>-1.2939</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5779</v>
+        <v>-1.4382</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7682</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O22" t="n">
         <v>-0.8097</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1488</v>
+        <v>2.5395</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4849</v>
+        <v>0.3054</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0185</v>
+        <v>0.3454</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5034</v>
+        <v>-0.04</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2772</v>
+        <v>2.3824</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.3824</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>E. SIMS SERRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,235 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>1.9134</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3.3018</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-1.3885</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.9412</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.8212</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.1703</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.8882</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.2821</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.2291</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.7682</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.5391</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.9301</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.0481</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.4404</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.4885</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-3.9331</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-0.3321</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-3.601</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>O. SUBIRANAS CASELLAS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.5328000000000001</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.3298</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.9358</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.7874</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.1484</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.6421</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.0192</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.6613</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.5779</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.7682</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.8097</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.4849</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.5034</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484305_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>20.9751</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E25" t="n">
         <v>15.1488</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F25" t="n">
         <v>5.826099999999999</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G25" t="n">
         <v>8.1417</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H25" t="n">
         <v>5.4414</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I25" t="n">
         <v>2.7005</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J25" t="n">
         <v>18.5242</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K25" t="n">
         <v>14.4716</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L25" t="n">
         <v>4.0525</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M25" t="n">
         <v>-10.3824</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N25" t="n">
         <v>-9.030200000000001</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O25" t="n">
         <v>-1.3521</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P25" t="n">
         <v>9.767099999999999</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q25" t="n">
         <v>-11.7204</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>21.4878</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S25" t="n">
         <v>1.1833</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T25" t="n">
         <v>1.1979</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U25" t="n">
         <v>-0.01470000000000005</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V25" t="n">
         <v>1.8829</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W25" t="n">
         <v>7.1472</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X25" t="n">
         <v>-5.2643</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
